--- a/config/generated/templates/AbilityResourceDelta.xlsx
+++ b/config/generated/templates/AbilityResourceDelta.xlsx
@@ -704,8 +704,8 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
-      <formula1>"Energy,SkillPoints,Hp,CharacterResource"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource, TeamResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
+      <formula1>"Energy,SkillPoints,Hp,CharacterResource,TeamResource"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Spend, Reserve, Gain" promptTitle="ResourceDeltaKind enum" prompt="Select a value from the dropdown." sqref="F8:F1007">
       <formula1>"Spend,Reserve,Gain"</formula1>

--- a/config/generated/templates/AbilityResourceDelta.xlsx
+++ b/config/generated/templates/AbilityResourceDelta.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>97e346dc7045b2f3</t>
+    <t>c78486d4c5ca1b3b</t>
   </si>
   <si>
     <t>#name</t>
@@ -94,7 +94,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
